--- a/Data/FlightPlan/FPL_ 05 AUG.xlsx
+++ b/Data/FlightPlan/FPL_ 05 AUG.xlsx
@@ -575,255 +575,255 @@
     <t>15:55</t>
   </si>
   <si>
-    <t>17:49</t>
+    <t>19:53</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>09:12</t>
+  </si>
+  <si>
+    <t>11:46</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>13:47</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>19:12</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>08:58</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>10:51</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>12:49</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>18:44</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>18:42</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>00:40</t>
+  </si>
+  <si>
+    <t>VN-A537</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>14:09</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>18:13</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>20:52</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>10:44</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:47</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>12:41</t>
+  </si>
+  <si>
+    <t>14:37</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>19:21</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>21:00</t>
   </si>
   <si>
     <t>22:15</t>
   </si>
   <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>09:12</t>
-  </si>
-  <si>
-    <t>11:46</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>13:47</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>19:12</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>08:58</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>10:51</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>12:49</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>18:44</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>18:42</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>23:40</t>
-  </si>
-  <si>
-    <t>00:40</t>
-  </si>
-  <si>
-    <t>VN-A537</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>14:09</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>18:13</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>20:52</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>09:03</t>
-  </si>
-  <si>
-    <t>10:44</t>
-  </si>
-  <si>
-    <t>12:53</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>17:47</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>20:16</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>12:41</t>
-  </si>
-  <si>
-    <t>14:37</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>19:21</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
     <t>VN-A543</t>
   </si>
   <si>
@@ -977,6 +977,9 @@
     <t>VDH</t>
   </si>
   <si>
+    <t>20:02</t>
+  </si>
+  <si>
     <t>22:05</t>
   </si>
   <si>
@@ -1139,7 +1142,7 @@
     <t>16:18</t>
   </si>
   <si>
-    <t>20:31</t>
+    <t>20:23</t>
   </si>
   <si>
     <t>VN-A633</t>
@@ -1238,6 +1241,9 @@
     <t>13:06</t>
   </si>
   <si>
+    <t>19:54</t>
+  </si>
+  <si>
     <t>VN-A640</t>
   </si>
   <si>
@@ -1343,6 +1349,9 @@
     <t>09:29</t>
   </si>
   <si>
+    <t>19:48</t>
+  </si>
+  <si>
     <t>VN-A646</t>
   </si>
   <si>
@@ -1397,7 +1406,7 @@
     <t>16:46</t>
   </si>
   <si>
-    <t>20:03</t>
+    <t>20:17</t>
   </si>
   <si>
     <t>01:10</t>
@@ -1430,6 +1439,9 @@
     <t>PKX</t>
   </si>
   <si>
+    <t>00:26</t>
+  </si>
+  <si>
     <t>VN-A651</t>
   </si>
   <si>
@@ -1544,9 +1556,6 @@
     <t>17:39</t>
   </si>
   <si>
-    <t>20:25</t>
-  </si>
-  <si>
     <t>02:20</t>
   </si>
   <si>
@@ -1625,7 +1634,7 @@
     <t>13:27</t>
   </si>
   <si>
-    <t>21:02</t>
+    <t>20:58</t>
   </si>
   <si>
     <t>VN-A671</t>
@@ -1721,6 +1730,9 @@
     <t>18:06</t>
   </si>
   <si>
+    <t>20:26</t>
+  </si>
+  <si>
     <t>VN-A684</t>
   </si>
   <si>
@@ -1745,6 +1757,9 @@
     <t>15:42</t>
   </si>
   <si>
+    <t>20:21</t>
+  </si>
+  <si>
     <t>VN-A689</t>
   </si>
   <si>
@@ -1835,7 +1850,7 @@
     <t>00:10</t>
   </si>
   <si>
-    <t>00:04</t>
+    <t>23:59</t>
   </si>
   <si>
     <t>VN-A814</t>
@@ -1868,7 +1883,7 @@
     <t>Total Record(s): 447</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 05, 2026 18:25</t>
+    <t xml:space="preserve">Generated on  Aug 05, 2026 18:37</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3121,11 +3136,11 @@
         <v>79</v>
       </c>
       <c t="s" r="K29" s="7">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="L29" s="7"/>
       <c t="s" r="M29" s="7">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
@@ -4701,11 +4716,11 @@
         <v>63</v>
       </c>
       <c t="s" r="K79" s="7">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>189</v>
+        <v>147</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -5867,7 +5882,7 @@
       </c>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>257</v>
+        <v>25</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5897,14 +5912,14 @@
         <v>218</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c t="s" r="K116" s="7">
         <v>143</v>
       </c>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5934,7 +5949,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5946,7 +5961,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>178</v>
@@ -5969,7 +5984,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5978,10 +5993,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H119" s="8">
+        <v>261</v>
+      </c>
+      <c t="s" r="I119" s="7">
         <v>262</v>
-      </c>
-      <c t="s" r="I119" s="7">
-        <v>263</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>86</v>
@@ -5989,7 +6004,7 @@
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -6004,13 +6019,13 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>16</v>
@@ -6024,7 +6039,7 @@
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -6039,7 +6054,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -6048,7 +6063,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>101</v>
@@ -6074,13 +6089,13 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>16</v>
@@ -6096,7 +6111,7 @@
       </c>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -6111,7 +6126,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -6120,16 +6135,16 @@
         <v>16</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>124</v>
       </c>
       <c t="s" r="K123" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
@@ -6148,22 +6163,22 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I124" s="7">
+        <v>269</v>
+      </c>
+      <c t="s" r="J124" s="7">
         <v>270</v>
-      </c>
-      <c t="s" r="J124" s="7">
-        <v>189</v>
       </c>
       <c t="s" r="K124" s="7">
         <v>147</v>
@@ -6185,7 +6200,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -6242,7 +6257,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c t="s" r="I127" s="7">
         <v>29</v>
@@ -6274,7 +6289,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>31</v>
@@ -6426,7 +6441,7 @@
         <v>143</v>
       </c>
       <c t="s" r="K132" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
@@ -6615,7 +6630,7 @@
         <v>287</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -6967,7 +6982,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="I150" s="7">
         <v>305</v>
@@ -6999,7 +7014,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>31</v>
@@ -7087,7 +7102,7 @@
       </c>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -7282,7 +7297,9 @@
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
-      <c r="M159" s="7"/>
+      <c t="s" r="M159" s="7">
+        <v>322</v>
+      </c>
     </row>
     <row r="160" ht="15" customHeight="1">
       <c t="s" r="A160" s="6">
@@ -7308,17 +7325,17 @@
         <v>31</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c t="s" r="K160" s="7">
         <v>124</v>
       </c>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7345,7 +7362,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>151</v>
@@ -7381,7 +7398,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -7416,7 +7433,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7436,7 +7453,7 @@
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7451,7 +7468,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7460,7 +7477,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="I165" s="7">
         <v>297</v>
@@ -7484,22 +7501,22 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -7532,7 +7549,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7567,7 +7584,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7587,7 +7604,7 @@
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7602,7 +7619,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7611,7 +7628,7 @@
         <v>77</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="I170" s="7">
         <v>226</v>
@@ -7622,7 +7639,7 @@
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7637,13 +7654,13 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>77</v>
@@ -7657,7 +7674,7 @@
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7672,7 +7689,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7705,7 +7722,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7714,13 +7731,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -7753,7 +7770,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7773,7 +7790,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7788,7 +7805,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7808,7 +7825,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7823,7 +7840,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7832,7 +7849,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="I177" s="7">
         <v>170</v>
@@ -7843,7 +7860,7 @@
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7858,13 +7875,13 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>16</v>
@@ -7878,7 +7895,7 @@
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7893,7 +7910,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7913,7 +7930,7 @@
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7928,7 +7945,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7940,10 +7957,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7961,7 +7978,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7970,7 +7987,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="I181" s="7">
         <v>314</v>
@@ -8009,13 +8026,13 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>16</v>
@@ -8029,7 +8046,7 @@
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -8044,7 +8061,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -8079,7 +8096,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -8094,7 +8111,7 @@
         <v>221</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -8127,7 +8144,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8147,7 +8164,7 @@
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -8162,7 +8179,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -8182,7 +8199,7 @@
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -8197,7 +8214,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8212,7 +8229,7 @@
         <v>222</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -8245,7 +8262,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8257,15 +8274,15 @@
         <v>24</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8280,7 +8297,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -8292,7 +8309,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>18</v>
@@ -8300,7 +8317,7 @@
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8315,7 +8332,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8350,7 +8367,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8383,7 +8400,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8395,10 +8412,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -8431,7 +8448,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8466,7 +8483,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8486,7 +8503,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8501,7 +8518,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8534,7 +8551,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8543,7 +8560,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="I200" s="7">
         <v>54</v>
@@ -8582,7 +8599,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8602,7 +8619,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8617,7 +8634,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8639,7 +8656,7 @@
       </c>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8654,7 +8671,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8666,7 +8683,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>187</v>
@@ -8691,7 +8708,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8709,7 +8726,7 @@
         <v>75</v>
       </c>
       <c t="s" r="K205" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
@@ -8728,7 +8745,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8743,7 +8760,7 @@
         <v>238</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8761,7 +8778,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8776,7 +8793,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8809,7 +8826,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8821,7 +8838,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>152</v>
@@ -8829,7 +8846,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8844,7 +8861,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8879,7 +8896,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8894,12 +8911,12 @@
         <v>63</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8914,7 +8931,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8926,7 +8943,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>94</v>
@@ -8962,7 +8979,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8971,18 +8988,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8997,19 +9014,19 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>72</v>
@@ -9032,7 +9049,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -9050,11 +9067,11 @@
         <v>146</v>
       </c>
       <c t="s" r="K216" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -9069,7 +9086,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -9087,11 +9104,11 @@
         <v>39</v>
       </c>
       <c t="s" r="K217" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -9106,7 +9123,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -9158,7 +9175,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9173,12 +9190,12 @@
         <v>109</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9193,7 +9210,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -9202,10 +9219,10 @@
         <v>77</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>250</v>
@@ -9213,7 +9230,7 @@
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9228,13 +9245,13 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>77</v>
@@ -9263,7 +9280,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9272,7 +9289,7 @@
         <v>77</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="I223" s="7">
         <v>75</v>
@@ -9283,7 +9300,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9298,13 +9315,13 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>77</v>
@@ -9313,7 +9330,7 @@
         <v>220</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -9331,7 +9348,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9343,10 +9360,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -9379,7 +9396,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9391,15 +9408,15 @@
         <v>310</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -9414,7 +9431,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9426,7 +9443,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>155</v>
@@ -9449,7 +9466,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9461,10 +9478,10 @@
         <v>310</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -9484,7 +9501,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9506,7 +9523,7 @@
       </c>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9536,7 +9553,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9556,7 +9573,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9571,7 +9588,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9583,7 +9600,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>138</v>
@@ -9591,7 +9608,7 @@
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9606,7 +9623,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9615,7 +9632,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c t="s" r="I234" s="7">
         <v>215</v>
@@ -9626,7 +9643,7 @@
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9641,13 +9658,13 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>16</v>
@@ -9656,12 +9673,12 @@
         <v>298</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9676,7 +9693,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9691,14 +9708,14 @@
         <v>256</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c t="s" r="K236" s="7">
         <v>201</v>
       </c>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9713,7 +9730,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9735,7 +9752,7 @@
       </c>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9765,7 +9782,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9777,7 +9794,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>29</v>
@@ -9785,7 +9802,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9800,7 +9817,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9820,7 +9837,7 @@
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9835,7 +9852,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9844,7 +9861,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c t="s" r="I241" s="7">
         <v>114</v>
@@ -9855,7 +9872,7 @@
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9870,13 +9887,13 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>31</v>
@@ -9885,7 +9902,7 @@
         <v>226</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9905,7 +9922,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9925,7 +9942,7 @@
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9940,7 +9957,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9962,7 +9979,7 @@
       </c>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9977,7 +9994,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -10029,7 +10046,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -10041,15 +10058,15 @@
         <v>24</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -10064,7 +10081,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -10084,7 +10101,7 @@
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10099,7 +10116,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -10108,7 +10125,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="I249" s="7">
         <v>211</v>
@@ -10119,7 +10136,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -10134,13 +10151,13 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>16</v>
@@ -10169,7 +10186,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -10184,12 +10201,12 @@
         <v>298</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>218</v>
+        <v>410</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -10204,7 +10221,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -10219,14 +10236,14 @@
         <v>125</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c t="s" r="K252" s="7">
         <v>106</v>
       </c>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -10256,7 +10273,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10276,7 +10293,7 @@
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10291,7 +10308,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -10311,7 +10328,7 @@
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10326,7 +10343,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10361,7 +10378,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10379,7 +10396,7 @@
         <v>142</v>
       </c>
       <c t="s" r="K257" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
@@ -10398,7 +10415,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10420,7 +10437,7 @@
       </c>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10435,7 +10452,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -10444,7 +10461,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>168</v>
@@ -10483,7 +10500,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10495,7 +10512,7 @@
         <v>321</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>302</v>
@@ -10503,7 +10520,7 @@
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10518,7 +10535,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10538,7 +10555,7 @@
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10553,7 +10570,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10562,7 +10579,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="I263" s="7">
         <v>183</v>
@@ -10588,19 +10605,19 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>252</v>
@@ -10608,7 +10625,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10623,7 +10640,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10632,7 +10649,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="I265" s="7">
         <v>140</v>
@@ -10643,7 +10660,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10658,13 +10675,13 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>31</v>
@@ -10676,11 +10693,11 @@
         <v>287</v>
       </c>
       <c t="s" r="K266" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10695,7 +10712,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -10707,7 +10724,7 @@
         <v>251</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>26</v>
@@ -10717,7 +10734,7 @@
       </c>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10732,7 +10749,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10744,7 +10761,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>67</v>
@@ -10754,7 +10771,7 @@
       </c>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10784,7 +10801,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10804,7 +10821,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10819,7 +10836,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10834,12 +10851,12 @@
         <v>116</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10854,7 +10871,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10889,7 +10906,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10909,7 +10926,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10924,7 +10941,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10957,7 +10974,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -11005,7 +11022,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -11017,7 +11034,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J277" s="7">
         <v>207</v>
@@ -11025,7 +11042,7 @@
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -11040,7 +11057,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -11060,7 +11077,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -11075,7 +11092,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -11095,7 +11112,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -11110,7 +11127,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -11130,7 +11147,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -11145,7 +11162,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -11180,7 +11197,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -11213,7 +11230,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -11228,7 +11245,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -11261,7 +11278,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -11281,7 +11298,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -11296,7 +11313,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -11316,7 +11333,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11331,7 +11348,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -11351,7 +11368,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11366,7 +11383,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -11386,7 +11403,7 @@
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11401,7 +11418,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -11410,7 +11427,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c t="s" r="I289" s="7">
         <v>218</v>
@@ -11434,22 +11451,22 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -11482,7 +11499,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11497,12 +11514,12 @@
         <v>245</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11517,7 +11534,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11552,7 +11569,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11571,7 +11588,9 @@
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
-      <c r="M294" s="7"/>
+      <c t="s" r="M294" s="7">
+        <v>446</v>
+      </c>
     </row>
     <row r="295" ht="15" customHeight="1">
       <c t="s" r="A295" s="6">
@@ -11585,7 +11604,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -11597,10 +11616,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -11633,7 +11652,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -11642,7 +11661,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c t="s" r="I297" s="7">
         <v>113</v>
@@ -11653,7 +11672,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11668,27 +11687,27 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11703,7 +11722,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -11738,7 +11757,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11773,7 +11792,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11785,7 +11804,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>225</v>
@@ -11821,7 +11840,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11830,10 +11849,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>151</v>
@@ -11841,7 +11860,7 @@
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11856,13 +11875,13 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>31</v>
@@ -11876,7 +11895,7 @@
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11891,7 +11910,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11926,7 +11945,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11935,7 +11954,7 @@
         <v>82</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>19</v>
@@ -11946,7 +11965,7 @@
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11961,13 +11980,13 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>82</v>
@@ -11981,7 +12000,7 @@
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11996,7 +12015,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -12011,7 +12030,7 @@
         <v>218</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -12029,7 +12048,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -12038,13 +12057,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="I309" s="7">
         <v>147</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -12062,22 +12081,22 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -12110,7 +12129,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -12122,7 +12141,7 @@
         <v>277</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>113</v>
@@ -12130,7 +12149,7 @@
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -12145,7 +12164,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -12165,7 +12184,7 @@
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -12180,7 +12199,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -12195,12 +12214,12 @@
         <v>72</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -12215,7 +12234,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -12235,7 +12254,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12250,7 +12269,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -12272,7 +12291,7 @@
       </c>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12287,7 +12306,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -12296,13 +12315,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="I317" s="7">
         <v>312</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -12320,22 +12339,22 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
+        <v>458</v>
+      </c>
+      <c r="F318" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G318" s="8">
         <v>455</v>
-      </c>
-      <c r="F318" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G318" s="8">
-        <v>452</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -12368,7 +12387,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -12383,12 +12402,12 @@
         <v>113</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12403,7 +12422,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -12415,10 +12434,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -12438,7 +12457,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -12453,12 +12472,12 @@
         <v>274</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12473,7 +12492,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12485,15 +12504,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12508,7 +12527,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -12517,17 +12536,19 @@
         <v>31</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c t="s" r="I324" s="7">
         <v>105</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
-      <c r="M324" s="7"/>
+      <c t="s" r="M324" s="7">
+        <v>476</v>
+      </c>
     </row>
     <row r="325" ht="15" customHeight="1">
       <c t="s" r="A325" s="6">
@@ -12541,19 +12562,19 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>92</v>
@@ -12589,7 +12610,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -12604,7 +12625,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -12624,7 +12645,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -12644,7 +12665,7 @@
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12659,7 +12680,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12671,7 +12692,7 @@
         <v>251</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>209</v>
@@ -12694,7 +12715,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12729,7 +12750,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12741,7 +12762,7 @@
         <v>277</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>103</v>
@@ -12749,7 +12770,7 @@
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12764,7 +12785,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12784,7 +12805,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12799,7 +12820,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12814,7 +12835,7 @@
         <v>227</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c t="s" r="K333" s="7">
         <v>311</v>
@@ -12836,7 +12857,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12851,10 +12872,10 @@
         <v>106</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="K334" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
@@ -12888,7 +12909,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12923,7 +12944,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -12958,7 +12979,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12973,12 +12994,12 @@
         <v>104</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -13008,7 +13029,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -13020,7 +13041,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>157</v>
@@ -13028,7 +13049,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -13043,7 +13064,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -13058,12 +13079,12 @@
         <v>95</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -13078,7 +13099,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -13087,7 +13108,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>285</v>
@@ -13113,13 +13134,13 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>31</v>
@@ -13148,7 +13169,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -13168,7 +13189,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13183,7 +13204,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -13216,7 +13237,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -13231,7 +13252,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -13264,7 +13285,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -13273,10 +13294,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>29</v>
@@ -13284,7 +13305,7 @@
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -13299,13 +13320,13 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>31</v>
@@ -13319,7 +13340,7 @@
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -13334,7 +13355,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -13343,7 +13364,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c t="s" r="I350" s="7">
         <v>58</v>
@@ -13369,13 +13390,13 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>31</v>
@@ -13384,12 +13405,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13404,7 +13425,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -13424,7 +13445,7 @@
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -13439,7 +13460,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -13451,7 +13472,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>227</v>
@@ -13459,7 +13480,7 @@
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13474,7 +13495,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -13489,7 +13510,7 @@
         <v>297</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -13507,7 +13528,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -13555,7 +13576,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13564,13 +13585,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -13590,13 +13611,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>31</v>
@@ -13605,7 +13626,7 @@
         <v>283</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -13625,7 +13646,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13660,7 +13681,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13669,7 +13690,7 @@
         <v>82</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="I360" s="7">
         <v>217</v>
@@ -13680,7 +13701,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13695,22 +13716,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -13728,7 +13749,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13776,7 +13797,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -13796,7 +13817,7 @@
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13811,7 +13832,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -13826,12 +13847,12 @@
         <v>93</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13846,7 +13867,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -13855,18 +13876,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c t="s" r="I366" s="7">
         <v>303</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13881,13 +13902,13 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c t="s" r="H367" s="8">
         <v>16</v>
@@ -13916,7 +13937,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13936,7 +13957,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13951,7 +13972,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13966,7 +13987,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -14001,7 +14022,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -14036,7 +14057,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -14048,13 +14069,13 @@
         <v>31</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>126</v>
       </c>
       <c t="s" r="K372" s="7">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
@@ -14073,7 +14094,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -14082,20 +14103,20 @@
         <v>31</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c t="s" r="I373" s="7">
         <v>127</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c t="s" r="K373" s="7">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -14110,22 +14131,22 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c t="s" r="K374" s="7">
         <v>107</v>
@@ -14162,7 +14183,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -14174,15 +14195,15 @@
         <v>82</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -14197,7 +14218,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -14209,10 +14230,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -14232,7 +14253,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -14244,7 +14265,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>274</v>
@@ -14254,7 +14275,7 @@
       </c>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -14269,7 +14290,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -14284,14 +14305,14 @@
         <v>212</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="K379" s="7">
         <v>137</v>
       </c>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14306,7 +14327,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -14315,10 +14336,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>104</v>
@@ -14326,7 +14347,7 @@
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -14341,13 +14362,13 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>16</v>
@@ -14356,7 +14377,7 @@
         <v>219</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>511</v>
+        <v>189</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -14374,7 +14395,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -14383,7 +14404,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c t="s" r="I382" s="7">
         <v>279</v>
@@ -14407,22 +14428,22 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -14455,7 +14476,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -14490,7 +14511,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -14502,7 +14523,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>211</v>
@@ -14510,7 +14531,7 @@
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14525,7 +14546,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -14537,10 +14558,10 @@
         <v>277</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -14560,7 +14581,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -14580,7 +14601,7 @@
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14595,7 +14616,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14604,10 +14625,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>162</v>
@@ -14617,7 +14638,7 @@
       </c>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14632,13 +14653,13 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>31</v>
@@ -14654,7 +14675,7 @@
       </c>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14684,7 +14705,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14699,7 +14720,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -14719,7 +14740,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14731,7 +14752,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>183</v>
@@ -14739,7 +14760,7 @@
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14754,7 +14775,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -14766,7 +14787,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>34</v>
@@ -14789,7 +14810,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -14826,7 +14847,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -14859,7 +14880,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -14871,7 +14892,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>312</v>
@@ -14907,7 +14928,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14919,7 +14940,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>302</v>
@@ -14927,7 +14948,7 @@
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14942,7 +14963,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14962,7 +14983,7 @@
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14977,7 +14998,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -15012,7 +15033,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -15034,7 +15055,7 @@
       </c>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -15049,7 +15070,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -15064,7 +15085,7 @@
         <v>253</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c t="s" r="K403" s="7">
         <v>39</v>
@@ -15101,7 +15122,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
@@ -15121,7 +15142,7 @@
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -15136,7 +15157,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
@@ -15158,7 +15179,7 @@
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15173,7 +15194,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -15193,7 +15214,7 @@
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -15208,7 +15229,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -15228,7 +15249,7 @@
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -15243,7 +15264,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
@@ -15258,7 +15279,7 @@
         <v>255</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -15293,7 +15314,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -15302,7 +15323,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c t="s" r="I411" s="7">
         <v>206</v>
@@ -15313,7 +15334,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -15328,19 +15349,19 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>95</v>
@@ -15348,7 +15369,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15363,7 +15384,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -15375,7 +15396,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>19</v>
@@ -15383,7 +15404,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15398,7 +15419,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -15413,12 +15434,12 @@
         <v>36</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15433,7 +15454,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -15448,11 +15469,15 @@
         <v>255</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>268</v>
-      </c>
-      <c r="K415" s="7"/>
+        <v>267</v>
+      </c>
+      <c t="s" r="K415" s="7">
+        <v>65</v>
+      </c>
       <c r="L415" s="7"/>
-      <c r="M415" s="7"/>
+      <c t="s" r="M415" s="7">
+        <v>424</v>
+      </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
       <c t="s" r="A416" s="6">
@@ -15466,7 +15491,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -15503,7 +15528,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -15512,10 +15537,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>58</v>
@@ -15551,7 +15576,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -15563,7 +15588,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>153</v>
@@ -15586,7 +15611,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -15601,7 +15626,7 @@
         <v>225</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -15621,7 +15646,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -15633,7 +15658,7 @@
         <v>191</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>211</v>
@@ -15641,7 +15666,7 @@
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15656,7 +15681,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -15668,7 +15693,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>214</v>
@@ -15676,7 +15701,7 @@
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -15691,7 +15716,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -15726,7 +15751,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -15738,7 +15763,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>126</v>
@@ -15746,7 +15771,7 @@
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -15776,7 +15801,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
@@ -15796,7 +15821,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15811,7 +15836,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -15831,7 +15856,7 @@
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -15846,7 +15871,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -15855,7 +15880,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="I428" s="7">
         <v>113</v>
@@ -15864,11 +15889,11 @@
         <v>179</v>
       </c>
       <c t="s" r="K428" s="7">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -15883,13 +15908,13 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="H429" s="8">
         <v>31</v>
@@ -15901,11 +15926,11 @@
         <v>194</v>
       </c>
       <c t="s" r="K429" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -15920,7 +15945,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F430" s="7">
         <v>320</v>
@@ -15935,7 +15960,7 @@
         <v>196</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -15955,7 +15980,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -15967,10 +15992,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -15990,7 +16015,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
@@ -16002,10 +16027,10 @@
         <v>100</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -16023,7 +16048,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F433" s="7">
         <v>320</v>
@@ -16038,7 +16063,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -16071,7 +16096,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F435" s="7">
         <v>320</v>
@@ -16083,10 +16108,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -16106,7 +16131,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F436" s="7">
         <v>320</v>
@@ -16126,7 +16151,7 @@
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -16141,7 +16166,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F437" s="7">
         <v>320</v>
@@ -16153,7 +16178,7 @@
         <v>251</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c t="s" r="J437" s="7">
         <v>214</v>
@@ -16178,7 +16203,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F438" s="7">
         <v>320</v>
@@ -16190,17 +16215,17 @@
         <v>31</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="J438" s="7">
         <v>120</v>
       </c>
       <c t="s" r="K438" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -16215,7 +16240,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F439" s="7">
         <v>320</v>
@@ -16224,10 +16249,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c t="s" r="J439" s="7">
         <v>219</v>
@@ -16250,19 +16275,19 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F440" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="H440" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c t="s" r="J440" s="7">
         <v>78</v>
@@ -16298,7 +16323,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -16320,7 +16345,7 @@
       </c>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -16335,7 +16360,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -16344,7 +16369,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="I443" s="7">
         <v>214</v>
@@ -16355,7 +16380,7 @@
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -16370,27 +16395,27 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -16405,7 +16430,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
@@ -16438,7 +16463,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -16450,7 +16475,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>40</v>
@@ -16486,7 +16511,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
@@ -16506,7 +16531,7 @@
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -16521,7 +16546,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -16541,7 +16566,7 @@
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -16556,7 +16581,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="F450" s="7">
         <v>321</v>
@@ -16565,7 +16590,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H450" s="8">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c t="s" r="I450" s="7">
         <v>252</v>
@@ -16576,7 +16601,7 @@
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
       <c t="s" r="M450" s="7">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
@@ -16591,13 +16616,13 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="F451" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G451" s="8">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c t="s" r="H451" s="8">
         <v>31</v>
@@ -16606,7 +16631,7 @@
         <v>218</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -16639,7 +16664,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
@@ -16651,7 +16676,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c t="s" r="J453" s="7">
         <v>272</v>
@@ -16659,7 +16684,7 @@
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -16674,7 +16699,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F454" s="7">
         <v>320</v>
@@ -16694,7 +16719,7 @@
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
@@ -16709,7 +16734,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
@@ -16729,7 +16754,7 @@
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -16744,7 +16769,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F456" s="7">
         <v>320</v>
@@ -16764,7 +16789,7 @@
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
       <c t="s" r="M456" s="7">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="457" ht="14.25" customHeight="1">
@@ -16779,7 +16804,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F457" s="7">
         <v>320</v>
@@ -16788,7 +16813,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H457" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="I457" s="7">
         <v>187</v>
@@ -16814,13 +16839,13 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F458" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G458" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="H458" s="8">
         <v>16</v>
@@ -16829,7 +16854,7 @@
         <v>255</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c t="s" r="K458" s="7">
         <v>297</v>
@@ -16851,7 +16876,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F459" s="7">
         <v>320</v>
@@ -16860,20 +16885,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H459" s="8">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c t="s" r="J459" s="7">
         <v>314</v>
       </c>
       <c t="s" r="K459" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L459" s="7"/>
       <c t="s" r="M459" s="7">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="460" ht="15" customHeight="1">
@@ -16888,13 +16913,13 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F460" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G460" s="8">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c t="s" r="H460" s="8">
         <v>16</v>
@@ -16903,14 +16928,14 @@
         <v>240</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c t="s" r="K460" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L460" s="7"/>
       <c t="s" r="M460" s="7">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="461" ht="14.25" customHeight="1">
@@ -16940,7 +16965,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F462" s="7">
         <v>321</v>
@@ -16960,7 +16985,7 @@
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
       <c t="s" r="M462" s="7">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="463" ht="14.25" customHeight="1">
@@ -16975,7 +17000,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F463" s="7">
         <v>321</v>
@@ -16990,7 +17015,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -17010,7 +17035,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
@@ -17022,7 +17047,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c t="s" r="J464" s="7">
         <v>227</v>
@@ -17030,7 +17055,7 @@
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
       <c t="s" r="M464" s="7">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="465" ht="15" customHeight="1">
@@ -17045,7 +17070,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F465" s="7">
         <v>321</v>
@@ -17065,7 +17090,7 @@
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
-        <v>376</v>
+        <v>573</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -17095,7 +17120,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="F467" s="7">
         <v>321</v>
@@ -17132,7 +17157,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="F468" s="7">
         <v>321</v>
@@ -17150,11 +17175,11 @@
         <v>165</v>
       </c>
       <c t="s" r="K468" s="7">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="L468" s="7"/>
       <c t="s" r="M468" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="469" ht="14.25" customHeight="1">
@@ -17169,7 +17194,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="F469" s="7">
         <v>321</v>
@@ -17202,7 +17227,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="F470" s="7">
         <v>321</v>
@@ -17214,10 +17239,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -17250,7 +17275,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F472" s="7">
         <v>321</v>
@@ -17262,7 +17287,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="J472" s="7">
         <v>157</v>
@@ -17270,7 +17295,7 @@
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
       <c t="s" r="M472" s="7">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="473" ht="14.25" customHeight="1">
@@ -17285,7 +17310,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F473" s="7">
         <v>321</v>
@@ -17300,14 +17325,14 @@
         <v>45</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c t="s" r="K473" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L473" s="7"/>
       <c t="s" r="M473" s="7">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="474" ht="14.25" customHeight="1">
@@ -17322,7 +17347,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F474" s="7">
         <v>321</v>
@@ -17344,7 +17369,7 @@
       </c>
       <c r="L474" s="7"/>
       <c t="s" r="M474" s="7">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="475" ht="15" customHeight="1">
@@ -17374,7 +17399,7 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="F476" s="7">
         <v>321</v>
@@ -17386,7 +17411,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I476" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J476" s="7">
         <v>272</v>
@@ -17394,7 +17419,7 @@
       <c r="K476" s="7"/>
       <c r="L476" s="7"/>
       <c t="s" r="M476" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="477" ht="14.25" customHeight="1">
@@ -17409,7 +17434,7 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="F477" s="7">
         <v>321</v>
@@ -17421,7 +17446,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I477" s="7">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c t="s" r="J477" s="7">
         <v>183</v>
@@ -17444,7 +17469,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="F478" s="7">
         <v>321</v>
@@ -17453,7 +17478,7 @@
         <v>100</v>
       </c>
       <c t="s" r="H478" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="I478" s="7">
         <v>283</v>
@@ -17464,7 +17489,7 @@
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
       <c t="s" r="M478" s="7">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="479" ht="14.25" customHeight="1">
@@ -17479,13 +17504,13 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="F479" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G479" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="H479" s="8">
         <v>100</v>
@@ -17494,12 +17519,12 @@
         <v>198</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
       <c t="s" r="M479" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="480" ht="15" customHeight="1">
@@ -17514,7 +17539,7 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="F480" s="7">
         <v>321</v>
@@ -17529,12 +17554,12 @@
         <v>162</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
       <c t="s" r="M480" s="7">
-        <v>368</v>
+        <v>582</v>
       </c>
     </row>
     <row r="481" ht="14.25" customHeight="1">
@@ -17549,7 +17574,7 @@
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="F481" s="7">
         <v>321</v>
@@ -17561,7 +17586,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I481" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c t="s" r="J481" s="7">
         <v>316</v>
@@ -17597,7 +17622,7 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="F483" s="7">
         <v>320</v>
@@ -17617,7 +17642,7 @@
       <c r="K483" s="7"/>
       <c r="L483" s="7"/>
       <c t="s" r="M483" s="7">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="484" ht="14.25" customHeight="1">
@@ -17632,7 +17657,7 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="F484" s="7">
         <v>320</v>
@@ -17654,7 +17679,7 @@
       </c>
       <c r="L484" s="7"/>
       <c t="s" r="M484" s="7">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="485" ht="15" customHeight="1">
@@ -17669,7 +17694,7 @@
       </c>
       <c r="D485" s="7"/>
       <c t="s" r="E485" s="7">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="F485" s="7">
         <v>320</v>
@@ -17678,7 +17703,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H485" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="I485" s="7">
         <v>138</v>
@@ -17689,7 +17714,7 @@
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
       <c t="s" r="M485" s="7">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="486" ht="14.25" customHeight="1">
@@ -17704,13 +17729,13 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="F486" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G486" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="H486" s="8">
         <v>16</v>
@@ -17719,7 +17744,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J486" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
@@ -17754,7 +17779,7 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="F488" s="7">
         <v>321</v>
@@ -17763,7 +17788,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H488" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="I488" s="7">
         <v>157</v>
@@ -17774,7 +17799,7 @@
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
       <c t="s" r="M488" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="489" ht="14.25" customHeight="1">
@@ -17789,13 +17814,13 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="F489" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G489" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="H489" s="8">
         <v>31</v>
@@ -17809,7 +17834,7 @@
       <c r="K489" s="7"/>
       <c r="L489" s="7"/>
       <c t="s" r="M489" s="7">
-        <v>583</v>
+        <v>588</v>
       </c>
     </row>
     <row r="490" ht="15" customHeight="1">
@@ -17824,7 +17849,7 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="F490" s="7">
         <v>321</v>
@@ -17833,7 +17858,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H490" s="8">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c t="s" r="I490" s="7">
         <v>311</v>
@@ -17857,22 +17882,22 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="F491" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G491" s="8">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c t="s" r="H491" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I491" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J491" s="7">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
@@ -17905,7 +17930,7 @@
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F493" s="7">
         <v>321</v>
@@ -17917,7 +17942,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I493" s="7">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c t="s" r="J493" s="7">
         <v>243</v>
@@ -17925,7 +17950,7 @@
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
       <c t="s" r="M493" s="7">
-        <v>587</v>
+        <v>592</v>
       </c>
     </row>
     <row r="494" ht="14.25" customHeight="1">
@@ -17940,7 +17965,7 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F494" s="7">
         <v>321</v>
@@ -17952,7 +17977,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I494" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c t="s" r="J494" s="7">
         <v>302</v>
@@ -17960,7 +17985,7 @@
       <c r="K494" s="7"/>
       <c r="L494" s="7"/>
       <c t="s" r="M494" s="7">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="495" ht="15" customHeight="1">
@@ -17975,7 +18000,7 @@
       </c>
       <c r="D495" s="7"/>
       <c t="s" r="E495" s="7">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F495" s="7">
         <v>321</v>
@@ -18010,7 +18035,7 @@
       </c>
       <c r="D496" s="7"/>
       <c t="s" r="E496" s="7">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F496" s="7">
         <v>321</v>
@@ -18025,7 +18050,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J496" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K496" s="7"/>
       <c r="L496" s="7"/>
@@ -18045,7 +18070,7 @@
       </c>
       <c r="D497" s="7"/>
       <c t="s" r="E497" s="7">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F497" s="7">
         <v>321</v>
@@ -18065,7 +18090,7 @@
       <c r="K497" s="7"/>
       <c r="L497" s="7"/>
       <c t="s" r="M497" s="7">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="498" ht="14.25" customHeight="1">
@@ -18080,7 +18105,7 @@
       </c>
       <c r="D498" s="7"/>
       <c t="s" r="E498" s="7">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F498" s="7">
         <v>321</v>
@@ -18128,7 +18153,7 @@
       </c>
       <c r="D500" s="7"/>
       <c t="s" r="E500" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F500" s="7">
         <v>321</v>
@@ -18137,13 +18162,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H500" s="8">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c t="s" r="I500" s="7">
         <v>244</v>
       </c>
       <c t="s" r="J500" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K500" s="7"/>
       <c r="L500" s="7"/>
@@ -18163,13 +18188,13 @@
       </c>
       <c r="D501" s="7"/>
       <c t="s" r="E501" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F501" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G501" s="8">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c t="s" r="H501" s="8">
         <v>16</v>
@@ -18178,12 +18203,12 @@
         <v>212</v>
       </c>
       <c t="s" r="J501" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K501" s="7"/>
       <c r="L501" s="7"/>
       <c t="s" r="M501" s="7">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="502" ht="14.25" customHeight="1">
@@ -18198,7 +18223,7 @@
       </c>
       <c r="D502" s="7"/>
       <c t="s" r="E502" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F502" s="7">
         <v>321</v>
@@ -18213,7 +18238,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J502" s="7">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K502" s="7"/>
       <c r="L502" s="7"/>
@@ -18233,7 +18258,7 @@
       </c>
       <c r="D503" s="7"/>
       <c t="s" r="E503" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F503" s="7">
         <v>321</v>
@@ -18253,7 +18278,7 @@
       <c r="K503" s="7"/>
       <c r="L503" s="7"/>
       <c t="s" r="M503" s="7">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="504" ht="14.25" customHeight="1">
@@ -18268,7 +18293,7 @@
       </c>
       <c r="D504" s="7"/>
       <c t="s" r="E504" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F504" s="7">
         <v>321</v>
@@ -18280,13 +18305,13 @@
         <v>77</v>
       </c>
       <c t="s" r="I504" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c t="s" r="J504" s="7">
         <v>279</v>
       </c>
       <c t="s" r="K504" s="7">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L504" s="7"/>
       <c t="s" r="M504" s="7">
@@ -18305,7 +18330,7 @@
       </c>
       <c r="D505" s="7"/>
       <c t="s" r="E505" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F505" s="7">
         <v>321</v>
@@ -18320,7 +18345,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J505" s="7">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c t="s" r="K505" s="7">
         <v>26</v>
@@ -18342,7 +18367,7 @@
       </c>
       <c r="D506" s="7"/>
       <c t="s" r="E506" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F506" s="7">
         <v>321</v>
@@ -18354,7 +18379,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I506" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c t="s" r="J506" s="7">
         <v>206</v>
@@ -18390,7 +18415,7 @@
       </c>
       <c r="D508" s="7"/>
       <c t="s" r="E508" s="7">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F508" s="7">
         <v>320</v>
@@ -18405,12 +18430,12 @@
         <v>109</v>
       </c>
       <c t="s" r="J508" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K508" s="7"/>
       <c r="L508" s="7"/>
       <c t="s" r="M508" s="7">
-        <v>594</v>
+        <v>599</v>
       </c>
     </row>
     <row r="509" ht="14.25" customHeight="1">
@@ -18425,7 +18450,7 @@
       </c>
       <c r="D509" s="7"/>
       <c t="s" r="E509" s="7">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F509" s="7">
         <v>320</v>
@@ -18437,7 +18462,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I509" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="J509" s="7">
         <v>156</v>
@@ -18445,7 +18470,7 @@
       <c r="K509" s="7"/>
       <c r="L509" s="7"/>
       <c t="s" r="M509" s="7">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="510" ht="15" customHeight="1">
@@ -18460,7 +18485,7 @@
       </c>
       <c r="D510" s="7"/>
       <c t="s" r="E510" s="7">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F510" s="7">
         <v>320</v>
@@ -18495,7 +18520,7 @@
       </c>
       <c r="D511" s="7"/>
       <c t="s" r="E511" s="7">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F511" s="7">
         <v>320</v>
@@ -18504,7 +18529,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H511" s="8">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c t="s" r="I511" s="7">
         <v>103</v>
@@ -18532,13 +18557,13 @@
       </c>
       <c r="D512" s="7"/>
       <c t="s" r="E512" s="7">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F512" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G512" s="8">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c t="s" r="H512" s="8">
         <v>31</v>
@@ -18569,7 +18594,7 @@
       </c>
       <c r="D513" s="7"/>
       <c t="s" r="E513" s="7">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F513" s="7">
         <v>320</v>
@@ -18578,7 +18603,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H513" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="I513" s="7">
         <v>218</v>
@@ -18587,7 +18612,7 @@
         <v>78</v>
       </c>
       <c t="s" r="K513" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L513" s="7"/>
       <c t="s" r="M513" s="7">
@@ -18606,13 +18631,13 @@
       </c>
       <c r="D514" s="7"/>
       <c t="s" r="E514" s="7">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F514" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G514" s="8">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="H514" s="8">
         <v>31</v>
@@ -18621,14 +18646,14 @@
         <v>220</v>
       </c>
       <c t="s" r="J514" s="7">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c t="s" r="K514" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L514" s="7"/>
       <c t="s" r="M514" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="515" ht="15" customHeight="1">
@@ -18658,13 +18683,13 @@
       </c>
       <c r="D516" s="7"/>
       <c t="s" r="E516" s="7">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="F516" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G516" s="8">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c t="s" r="H516" s="8">
         <v>82</v>
@@ -18673,12 +18698,12 @@
         <v>109</v>
       </c>
       <c t="s" r="J516" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K516" s="7"/>
       <c r="L516" s="7"/>
       <c t="s" r="M516" s="7">
-        <v>598</v>
+        <v>603</v>
       </c>
     </row>
     <row r="517" ht="14.25" customHeight="1">
@@ -18693,7 +18718,7 @@
       </c>
       <c r="D517" s="7"/>
       <c t="s" r="E517" s="7">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="F517" s="7">
         <v>330</v>
@@ -18715,7 +18740,7 @@
       </c>
       <c r="L517" s="7"/>
       <c t="s" r="M517" s="7">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="518" ht="14.25" customHeight="1">
@@ -18730,7 +18755,7 @@
       </c>
       <c r="D518" s="7"/>
       <c t="s" r="E518" s="7">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="F518" s="7">
         <v>330</v>
@@ -18742,17 +18767,17 @@
         <v>82</v>
       </c>
       <c t="s" r="I518" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c t="s" r="J518" s="7">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c t="s" r="K518" s="7">
         <v>222</v>
       </c>
       <c r="L518" s="7"/>
       <c t="s" r="M518" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="519" ht="14.25" customHeight="1">
@@ -18782,7 +18807,7 @@
       </c>
       <c r="D520" s="7"/>
       <c t="s" r="E520" s="7">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="F520" s="7">
         <v>330</v>
@@ -18797,12 +18822,12 @@
         <v>207</v>
       </c>
       <c t="s" r="J520" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K520" s="7"/>
       <c r="L520" s="7"/>
       <c t="s" r="M520" s="7">
-        <v>601</v>
+        <v>606</v>
       </c>
     </row>
     <row r="521" ht="14.25" customHeight="1">
@@ -18817,7 +18842,7 @@
       </c>
       <c r="D521" s="7"/>
       <c t="s" r="E521" s="7">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="F521" s="7">
         <v>330</v>
@@ -18837,7 +18862,7 @@
       <c r="K521" s="7"/>
       <c r="L521" s="7"/>
       <c t="s" r="M521" s="7">
-        <v>602</v>
+        <v>607</v>
       </c>
     </row>
     <row r="522" ht="14.25" customHeight="1">
@@ -18852,7 +18877,7 @@
       </c>
       <c r="D522" s="7"/>
       <c t="s" r="E522" s="7">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="F522" s="7">
         <v>330</v>
@@ -18861,10 +18886,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H522" s="8">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c t="s" r="I522" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c t="s" r="J522" s="7">
         <v>153</v>
@@ -18900,7 +18925,7 @@
       </c>
       <c r="D524" s="7"/>
       <c t="s" r="E524" s="7">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="F524" s="7">
         <v>330</v>
@@ -18909,7 +18934,7 @@
         <v>77</v>
       </c>
       <c t="s" r="H524" s="8">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c t="s" r="I524" s="7">
         <v>170</v>
@@ -18920,7 +18945,7 @@
       <c r="K524" s="7"/>
       <c r="L524" s="7"/>
       <c t="s" r="M524" s="7">
-        <v>606</v>
+        <v>611</v>
       </c>
     </row>
     <row r="525" ht="15" customHeight="1">
@@ -18935,13 +18960,13 @@
       </c>
       <c r="D525" s="7"/>
       <c t="s" r="E525" s="7">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="F525" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G525" s="8">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c t="s" r="H525" s="8">
         <v>77</v>
@@ -18950,12 +18975,12 @@
         <v>308</v>
       </c>
       <c t="s" r="J525" s="7">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="K525" s="7"/>
       <c r="L525" s="7"/>
       <c t="s" r="M525" s="7">
-        <v>608</v>
+        <v>613</v>
       </c>
     </row>
     <row r="526" ht="14.25" customHeight="1">
@@ -18985,7 +19010,7 @@
       </c>
       <c r="D527" s="7"/>
       <c t="s" r="E527" s="7">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="F527" s="7">
         <v>330</v>
@@ -19005,7 +19030,7 @@
       <c r="K527" s="7"/>
       <c r="L527" s="7"/>
       <c t="s" r="M527" s="7">
-        <v>610</v>
+        <v>615</v>
       </c>
     </row>
     <row r="528" ht="14.25" customHeight="1">
@@ -19020,7 +19045,7 @@
       </c>
       <c r="D528" s="7"/>
       <c t="s" r="E528" s="7">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="F528" s="7">
         <v>330</v>
@@ -19029,7 +19054,7 @@
         <v>77</v>
       </c>
       <c t="s" r="H528" s="8">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c t="s" r="I528" s="7">
         <v>187</v>
@@ -19040,7 +19065,7 @@
       <c r="K528" s="7"/>
       <c r="L528" s="7"/>
       <c t="s" r="M528" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="529" ht="14.25" customHeight="1">
@@ -19055,13 +19080,13 @@
       </c>
       <c r="D529" s="7"/>
       <c t="s" r="E529" s="7">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="F529" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G529" s="8">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c t="s" r="H529" s="8">
         <v>77</v>
@@ -19103,7 +19128,7 @@
       </c>
       <c r="D531" s="7"/>
       <c t="s" r="E531" s="7">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="F531" s="7">
         <v>330</v>
@@ -19118,7 +19143,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J531" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K531" s="7"/>
       <c r="L531" s="7"/>
@@ -19138,7 +19163,7 @@
       </c>
       <c r="D532" s="7"/>
       <c t="s" r="E532" s="7">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="F532" s="7">
         <v>330</v>
@@ -19147,7 +19172,7 @@
         <v>77</v>
       </c>
       <c t="s" r="H532" s="8">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c t="s" r="I532" s="7">
         <v>252</v>
@@ -19158,7 +19183,7 @@
       <c r="K532" s="7"/>
       <c r="L532" s="7"/>
       <c t="s" r="M532" s="7">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="533" ht="14.25" customHeight="1">
@@ -19173,13 +19198,13 @@
       </c>
       <c r="D533" s="7"/>
       <c t="s" r="E533" s="7">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="F533" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G533" s="8">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c t="s" r="H533" s="8">
         <v>77</v>
@@ -19221,13 +19246,13 @@
       </c>
       <c r="D535" s="7"/>
       <c t="s" r="E535" s="7">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="F535" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G535" s="8">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c t="s" r="H535" s="8">
         <v>31</v>
@@ -19271,7 +19296,7 @@
       </c>
       <c r="D537" s="7"/>
       <c t="s" r="E537" s="7">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="F537" s="7">
         <v>330</v>
@@ -19280,13 +19305,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H537" s="8">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c t="s" r="I537" s="7">
         <v>179</v>
       </c>
       <c t="s" r="J537" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K537" s="7"/>
       <c r="L537" s="7"/>
@@ -19306,13 +19331,13 @@
       </c>
       <c r="D538" s="7"/>
       <c t="s" r="E538" s="7">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="F538" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G538" s="8">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c t="s" r="H538" s="8">
         <v>31</v>
@@ -19329,7 +19354,7 @@
     </row>
     <row r="539" ht="15.75" customHeight="1">
       <c t="s" r="A539" s="9">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="B539" s="9"/>
       <c r="C539" s="9"/>
@@ -19349,7 +19374,7 @@
     <row r="540" ht="66" customHeight="1"/>
     <row r="541" ht="16.5" customHeight="1">
       <c t="s" r="A541" s="10">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B541" s="10"/>
       <c r="C541" s="10"/>
@@ -19362,7 +19387,7 @@
       <c r="J541" s="10"/>
       <c r="K541" s="10"/>
       <c t="s" r="L541" s="11">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="M541" s="11"/>
       <c r="N541" s="11"/>
